--- a/artfynd/A 27295-2024 artfynd.xlsx
+++ b/artfynd/A 27295-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96202786</v>
+        <v>96202846</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Aborrttjärn, Ång</t>
+          <t>Abbortjärn, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688475.4079975176</v>
+        <v>688337</v>
       </c>
       <c r="R2" t="n">
-        <v>7092022.86176397</v>
+        <v>7092143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-05-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96202846</v>
+        <v>96202786</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,14 +814,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Abbortjärn, Ång</t>
+          <t>Aborrttjärn, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688336.9066711601</v>
+        <v>688476</v>
       </c>
       <c r="R3" t="n">
-        <v>7092143.370187139</v>
+        <v>7092023</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2021-05-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
